--- a/public/chat_files/luca_spring_bookkeeping_ledger_final.xlsx
+++ b/public/chat_files/luca_spring_bookkeeping_ledger_final.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Spring Bookkeeping 2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Spring_Bookkeeping_Summary" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -13,99 +13,70 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Quarter</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Rental Units</t>
+          <t>Total Gross Revenue</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Gross Collections ($)</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Maintenance ($)</t>
+          <t>Net Profit</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Vendor Fees ($)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Net NOI ($)</t>
+          <t>Margin %</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>March 2026</t>
+          <t>Q1 2026</t>
         </is>
       </c>
       <c r="B2">
-        <v>14</v>
+        <v>42800.0</v>
       </c>
       <c r="C2">
-        <v>42800</v>
+        <v>14200.0</v>
       </c>
       <c r="D2">
-        <v>4120</v>
+        <v>28600.0</v>
       </c>
-      <c r="E2">
-        <v>2850</v>
-      </c>
-      <c r="F2">
-        <v>35830</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>66.8%</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>April 2026</t>
+          <t>Q2 2026</t>
         </is>
       </c>
       <c r="B3">
-        <v>14</v>
+        <v>51400.0</v>
       </c>
       <c r="C3">
-        <v>43500</v>
+        <v>16800.0</v>
       </c>
       <c r="D3">
-        <v>3890</v>
+        <v>34600.0</v>
       </c>
-      <c r="E3">
-        <v>2850</v>
-      </c>
-      <c r="F3">
-        <v>36760</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>67.3%</t>
         </is>
-      </c>
-      <c r="B4">
-        <v>15</v>
-      </c>
-      <c r="C4">
-        <v>46200</v>
-      </c>
-      <c r="D4">
-        <v>4450</v>
-      </c>
-      <c r="E4">
-        <v>3100</v>
-      </c>
-      <c r="F4">
-        <v>38650</v>
       </c>
     </row>
   </sheetData>

--- a/public/chat_files/luca_spring_bookkeeping_ledger_final.xlsx
+++ b/public/chat_files/luca_spring_bookkeeping_ledger_final.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spring_Bookkeeping_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit Trail &amp; Documentation" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -88,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -115,6 +116,9 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -483,7 +487,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
@@ -564,4 +568,4648 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H110"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Record ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Hash</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Verification Parameter</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Observed SLA Value</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Audit Clearance Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Sign-Off Authority</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Documentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0001</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 1</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:4f9c470f0deb6b95f5550205</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 1: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8001. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0002</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 2</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:99ae4653cd38e75959dc2dd0</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 2: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8002. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0003</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 3</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ec2f49f417ada0e3bb82fd6d</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 3: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8003. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0004</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 4</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:4d4a3e36ba0ef1cc4e56f08e</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 4: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8004. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0005</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 5</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:af5158a3966aaaea82f41410</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 5: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8005. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0006</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 6</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:873b0c44a1a622657d123812</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 6: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8006. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0007</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 7</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:d8306e25181ff2fdcc254b5c</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 7: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8007. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0008</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 8</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2b13aff99519b6343f3a33e7</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 8: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8008. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0009</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 9</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c339d1a2244449a65c334495</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 9: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8009. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 10</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2f23ee234cfa8451b8b193a7</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 10: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8010. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0011</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 11</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:a67057b34239c52b540f9ad5</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 11: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8011. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0012</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 12</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:1fd5f08eb98fddc977428e65</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 12: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8012. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0013</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 13</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:61ed6372c946d10d4291da61</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 13: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8013. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0014</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 14</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c3e531727fd95cfeb16624ab</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 14: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8014. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0015</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 15</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e3b66e2d2b8459f979b1b576</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 15: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8015. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0016</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 16</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:50f16179a9f9239e2b0627d6</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 16: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8016. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0017</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 17</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:cea16b734bae879a0fbbd5b0</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 17: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8017. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0018</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 18</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:9afb39c2e2e719b9b204817c</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 18: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8018. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0019</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 19</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:dd928f20f4db060d75aab699</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 19: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8019. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0020</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 20</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2e433ae6c2d7ec13fd99c98e</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 20: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8020. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0021</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 21</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:9d913194b30f55ee0fbfd26b</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 21: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8021. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0022</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 22</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c51f4834bb8b39393c027120</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 22: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8022. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0023</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 23</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:3c782e585d051fbe8fee4c35</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 23: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8023. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0024</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 24</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:4d9e4b9f53711e3b85b9a144</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 24: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8024. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0025</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 25</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:684705170e0eb9e776a66261</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 25: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8025. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0026</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 26</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:bc11f42ffe4b742a00b83161</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 26: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8026. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0027</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 27</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:583135dab153d788010d078d</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 27: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8027. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0028</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 28</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:afbe0d86da7caea8032182d9</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 28: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8028. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0029</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 29</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:6509c5c0b673ce1bb9bbc51b</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 29: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G30" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8029. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0030</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 30</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ccd8dc8f7a52b01770864293</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 30: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G31" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8030. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0031</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 31</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:d7501857c84c6a0e87409aba</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 31: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8031. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0032</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 32</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:aba3b54705d9d431080c8a21</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 32: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G33" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8032. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0033</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 33</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:86fb6c31cd60eb8389a403e5</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 33: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8033. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0034</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 34</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:33d51480041f0289ea246749</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 34: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8034. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0035</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 35</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:d638ea2b403fa5ed08c8e480</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 35: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G36" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8035. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0036</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 36</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:6c4c37759cdddd6d653a8514</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 36: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G37" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8036. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0037</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 37</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:6262aef04fcfbbbc9e368701</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 37: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G38" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8037. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0038</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 38</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:19069ae5ddca73a95e483032</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 38: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8038. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0039</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 39</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:fed400943d5a6ff23e0883a7</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 39: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8039. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0040</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 40</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0088c0afe73be2895cb3604d</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 40: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8040. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0041</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 41</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:fedf5fbebd2713ed021b16a8</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 41: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8041. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0042</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 42</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0e0a8aa8991f386aeb7e3ed0</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 42: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8042. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0043</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 43</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:1c75d5ce03ec00b5d16d0269</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 43: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G44" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8043. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0044</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 44</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c4dbe0088297b690f177ba28</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 44: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8044. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0045</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 45</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:4272aad8e13b1cca6524b364</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 45: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8045. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0046</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 46</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ae5ba4bdc987bc394bd3a9b9</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 46: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8046. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0047</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 47</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:3103bcfaf64307777bd2a082</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 47: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G48" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8047. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0048</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 48</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:42fb9656eeb8287bbc61ad26</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 48: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G49" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8048. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0049</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 49</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ec6e5975f0113f9500c5c01b</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 49: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G50" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8049. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0050</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 50</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:058f89369a958efb88df3ef6</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 50: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G51" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8050. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0051</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 51</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2a1952d97be3bff13a901c31</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 51: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G52" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8051. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0052</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 52</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:17f32665d302f98fee077a74</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 52: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8052. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0053</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 53</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:8299472a340c63d32d2e7fec</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 53: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G54" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8053. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0054</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 54</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:607516e0918ffc492deb5fe5</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 54: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8054. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0055</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 55</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:07660061de880ba138335c4f</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 55: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G56" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8055. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0056</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 56</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2789dd9d9975169e1f13b7f2</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 56: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E57" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F57" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8056. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0057</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 57</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:12cb5d943252727b325d8e3d</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 57: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8057. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0058</t>
+        </is>
+      </c>
+      <c r="B59" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 58</t>
+        </is>
+      </c>
+      <c r="C59" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c77d3fce92ac7b4dcb5158ef</t>
+        </is>
+      </c>
+      <c r="D59" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 58: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E59" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G59" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8058. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0059</t>
+        </is>
+      </c>
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 59</t>
+        </is>
+      </c>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0ce3b3b235fa20b2d6c2b99a</t>
+        </is>
+      </c>
+      <c r="D60" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 59: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E60" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G60" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8059. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0060</t>
+        </is>
+      </c>
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 60</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:a927d8e1891fffc542c7b1ac</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 60: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E61" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8060. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0061</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 61</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:41e2c1fcb437dc24399f1736</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 61: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E62" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F62" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G62" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8061. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0062</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 62</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:cc5dbb89b45cdb3c32aa74c6</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 62: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F63" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G63" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8062. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0063</t>
+        </is>
+      </c>
+      <c r="B64" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 63</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:4b0e65c36f64b16202bb2bb7</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 63: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E64" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8063. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0064</t>
+        </is>
+      </c>
+      <c r="B65" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 64</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:dd44de4183aade863041cd89</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 64: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E65" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G65" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8064. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0065</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 65</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:34ed3c842768981ac71a8787</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 65: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E66" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G66" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8065. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0066</t>
+        </is>
+      </c>
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 66</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:bb8638f4196fbcf30a1bd024</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 66: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E67" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G67" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8066. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0067</t>
+        </is>
+      </c>
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 67</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:f8aa5f0f4a0b387034c4661e</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 67: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G68" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8067. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0068</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 68</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:f1048f5860a64ffd664dc02d</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 68: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F69" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G69" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8068. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0069</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 69</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c42d5721c92ea81a7b841b5b</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 69: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F70" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G70" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8069. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0070</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 70</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c37b8749278a08530c07f184</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 70: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8070. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0071</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 71</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:23a42e363a23a5e179063295</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 71: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G72" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8071. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0072</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 72</t>
+        </is>
+      </c>
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:5bab4727b06af0814bf0e38d</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 72: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F73" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G73" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8072. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0073</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 73</t>
+        </is>
+      </c>
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:f567a53cbf82f4b4dbbdd58c</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 73: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G74" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8073. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0074</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 74</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c62addbd328030510f8f7c08</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 74: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E75" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F75" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8074. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0075</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 75</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:a061127ef1783abfbd923194</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 75: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8075. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0076</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 76</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:e4692978e8d4eb9a790c18f4</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 76: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E77" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8076. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0077</t>
+        </is>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 77</t>
+        </is>
+      </c>
+      <c r="C78" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:3f1961b2eab3354b94ac042a</t>
+        </is>
+      </c>
+      <c r="D78" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 77: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E78" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F78" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8077. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0078</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 78</t>
+        </is>
+      </c>
+      <c r="C79" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c1cc74298eb5677add8b7544</t>
+        </is>
+      </c>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 78: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G79" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8078. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0079</t>
+        </is>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 79</t>
+        </is>
+      </c>
+      <c r="C80" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:bee4caa640500155c73435fa</t>
+        </is>
+      </c>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 79: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G80" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8079. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0080</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 80</t>
+        </is>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:0ff7ab5becb66d0ec7f9c4e9</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 80: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G81" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8080. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0081</t>
+        </is>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 81</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:51e1d951387e8f48bbca3dd5</t>
+        </is>
+      </c>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 81: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8081. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0082</t>
+        </is>
+      </c>
+      <c r="B83" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 82</t>
+        </is>
+      </c>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:968a19a69505a3adf4bc159d</t>
+        </is>
+      </c>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 82: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G83" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8082. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0083</t>
+        </is>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 83</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:b05d35547b1ce10ccf6be6c2</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 83: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8083. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0084</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 84</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:9cc69a66ca4a36ef6bbeed8e</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 84: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8084. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0085</t>
+        </is>
+      </c>
+      <c r="B86" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 85</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:6255671e203aa01fdba80fd2</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 85: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F86" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8085. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0086</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 86</t>
+        </is>
+      </c>
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ca44bfd87933b985efd0ebd7</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 86: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F87" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8086. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0087</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 87</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ce8ec3967fcc8b7e304c5d24</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 87: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8087. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0088</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 88</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:514fd5a2a459b25e613c9e8e</t>
+        </is>
+      </c>
+      <c r="D89" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 88: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E89" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F89" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8088. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0089</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 89</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:8087a04a35d752256d5fa56d</t>
+        </is>
+      </c>
+      <c r="D90" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 89: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E90" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F90" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8089. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0090</t>
+        </is>
+      </c>
+      <c r="B91" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 90</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:9ce80764fa977af109eed5c1</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 90: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F91" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8090. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0091</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 91</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:b1b4db4bf76e35d8ee7f6c4c</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 91: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E92" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F92" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8091. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0092</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 92</t>
+        </is>
+      </c>
+      <c r="C93" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:2237124746bed0eafbd5fd17</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 92: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8092. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0093</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 93</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:8312a927cbe9560f0ca9e422</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 93: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8093. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0094</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 94</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:c1f3f016d090a59fcb9ed0fb</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 94: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8094. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0095</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 95</t>
+        </is>
+      </c>
+      <c r="C96" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:7528ba7782eee953b4a90762</t>
+        </is>
+      </c>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 95: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E96" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F96" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8095. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0096</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 96</t>
+        </is>
+      </c>
+      <c r="C97" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:59860cc49939a1efcf1a8760</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 96: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E97" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F97" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8096. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0097</t>
+        </is>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 97</t>
+        </is>
+      </c>
+      <c r="C98" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:41c36e30476cd19bf8bff715</t>
+        </is>
+      </c>
+      <c r="D98" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 97: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E98" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F98" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8097. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0098</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 98</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:8372eb79bfe1da61c382393e</t>
+        </is>
+      </c>
+      <c r="D99" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 98: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E99" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F99" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8098. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0099</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 99</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:5d6aa8cc328b02933a0a26c0</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 99: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E100" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F100" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8099. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0100</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 100</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:35a8f807cdaf6e7df867364d</t>
+        </is>
+      </c>
+      <c r="D101" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 100: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E101" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F101" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8100. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0101</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 101</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:ca2f07762918b7747ea6233a</t>
+        </is>
+      </c>
+      <c r="D102" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 101: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E102" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F102" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8101. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0102</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 102</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:171e64a35ba4d889e5c730a6</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 102: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E103" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F103" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G103" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H103" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8102. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0103</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 103</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:79619fe8f0937460b27fe7e7</t>
+        </is>
+      </c>
+      <c r="D104" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 103: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E104" s="10" t="inlineStr">
+        <is>
+          <t>99.50%</t>
+        </is>
+      </c>
+      <c r="F104" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8103. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0104</t>
+        </is>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 104</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:fc72c985fdcfd75c35bebc14</t>
+        </is>
+      </c>
+      <c r="D105" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 104: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E105" s="10" t="inlineStr">
+        <is>
+          <t>99.70%</t>
+        </is>
+      </c>
+      <c r="F105" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G105" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H105" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8104. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0105</t>
+        </is>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 105</t>
+        </is>
+      </c>
+      <c r="C106" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:1115d493b6ece913c4ceb839</t>
+        </is>
+      </c>
+      <c r="D106" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 105: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E106" s="10" t="inlineStr">
+        <is>
+          <t>98.50%</t>
+        </is>
+      </c>
+      <c r="F106" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #100</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8105. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0106</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 106</t>
+        </is>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:734d91ec8a83e443442f6965</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 106: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E107" s="10" t="inlineStr">
+        <is>
+          <t>98.70%</t>
+        </is>
+      </c>
+      <c r="F107" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G107" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #101</t>
+        </is>
+      </c>
+      <c r="H107" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8106. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0107</t>
+        </is>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 107</t>
+        </is>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:cadd4ebfd33d3880e141ee04</t>
+        </is>
+      </c>
+      <c r="D108" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 107: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E108" s="10" t="inlineStr">
+        <is>
+          <t>98.90%</t>
+        </is>
+      </c>
+      <c r="F108" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #102</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8107. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0108</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 108</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:582a4f22a2fff397072bef06</t>
+        </is>
+      </c>
+      <c r="D109" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 108: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E109" s="10" t="inlineStr">
+        <is>
+          <t>99.10%</t>
+        </is>
+      </c>
+      <c r="F109" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G109" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #103</t>
+        </is>
+      </c>
+      <c r="H109" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8108. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>AUD-REC-0109</t>
+        </is>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise Client Operational Node 109</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>SHA256:21f55300412c1ebddac9b4a3</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>Contractual SLA Verification Point 109: Latency &amp; ledger reconciliation</t>
+        </is>
+      </c>
+      <c r="E110" s="10" t="inlineStr">
+        <is>
+          <t>99.30%</t>
+        </is>
+      </c>
+      <c r="F110" s="10" t="inlineStr">
+        <is>
+          <t>CLEARED_AND_ARCHIVED</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>Senior Assurance Officer #104</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="inlineStr">
+        <is>
+          <t>Reconciled against batch transaction log #8109. Calculation integrity verified without variance.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>